--- a/Documents/Planning/output.xlsx
+++ b/Documents/Planning/output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Sakshi\Internship\CamDuct_KNND\Documents\Planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83CD2C39-0D01-46E5-99AE-DF089379FF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFF5E24-8DE5-4AB9-994C-E44F2B0A7208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A35A6B0-DF52-4FCB-9109-1F8540ABC412}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Sl.No</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>qty</t>
+  </si>
+  <si>
+    <t>status</t>
   </si>
 </sst>
 </file>
@@ -424,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3777FB-B89F-4647-9388-009AEFA76AF4}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.109375" customWidth="1"/>
@@ -433,7 +436,7 @@
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,6 +475,19 @@
       </c>
       <c r="M1" t="s">
         <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
